--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_146_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_146_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M2" t="n">
         <v>10</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>24</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
         <v>4</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>7</v>
@@ -2119,16 +2119,16 @@
         <v>23</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>6</v>
@@ -2511,7 +2511,7 @@
         <v>12</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2713,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
         <v>2</v>
@@ -3301,10 +3301,10 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X27" t="n">
         <v>2</v>
@@ -3827,16 +3827,16 @@
         <v>119</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X30" t="n">
         <v>30</v>
@@ -4292,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4687,13 +4687,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X37" t="n">
         <v>8</v>
@@ -5076,16 +5076,16 @@
         <v>18</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>2</v>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>2</v>
@@ -5670,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X42" t="n">
         <v>4</v>
@@ -6062,10 +6062,10 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X44" t="n">
         <v>4</v>
@@ -6784,16 +6784,16 @@
         <v>93</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X48" t="n">
         <v>25</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_146_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_146_EL.xlsx
@@ -674,10 +674,10 @@
         <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="P3" t="n">
         <v>7</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>80.65</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1543,10 +1543,10 @@
         <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -1935,10 +1935,10 @@
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -3307,10 +3307,10 @@
         <v>2</v>
       </c>
       <c r="X27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3503,14 +3503,14 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>7</v>
       </c>
       <c r="X30" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4696,14 +4696,14 @@
         <v>4</v>
       </c>
       <c r="X37" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5284,10 +5284,10 @@
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5676,14 +5676,14 @@
         <v>3</v>
       </c>
       <c r="X42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -6068,10 +6068,10 @@
         <v>2</v>
       </c>
       <c r="X44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>11</v>
       </c>
       <c r="X48" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="Y48" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA48" t="n">
